--- a/output_image/典型日2_09-25_汇总指标.xlsx
+++ b/output_image/典型日2_09-25_汇总指标.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>算法</t>
   </si>
@@ -25,6 +25,9 @@
     <t>平均光伏消纳率(%)</t>
   </si>
   <si>
+    <t>8:00-16:00时段光伏消纳率(%)</t>
+  </si>
+  <si>
     <t>峰值负荷(kW)</t>
   </si>
   <si>
@@ -40,6 +43,15 @@
     <t>总光伏发电量(kWh)</t>
   </si>
   <si>
+    <t>8:00-16:00时段总负荷电量(kWh)</t>
+  </si>
+  <si>
+    <t>8:00-16:00时段总光伏发电量(kWh)</t>
+  </si>
+  <si>
+    <t>8:00-16:00时段消纳光伏电量(kWh)</t>
+  </si>
+  <si>
     <t>EV总充电量(kWh)</t>
   </si>
   <si>
@@ -62,6 +74,9 @@
   </si>
   <si>
     <t>光伏消纳提升(%)</t>
+  </si>
+  <si>
+    <t>8:00-16:00时段光伏消纳提升(%)</t>
   </si>
   <si>
     <t>峰谷差降低率(%)</t>
@@ -437,10 +452,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,10 +507,25 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>697.3</v>
@@ -504,51 +534,66 @@
         <v>35.98</v>
       </c>
       <c r="D2">
+        <v>68.2</v>
+      </c>
+      <c r="E2">
         <v>210.27</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>51.04</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>159.23</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>2472.89</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1226.06005859375</v>
       </c>
-      <c r="I2">
+      <c r="J2">
+        <v>769.1900000000001</v>
+      </c>
+      <c r="K2">
+        <v>1114.55</v>
+      </c>
+      <c r="L2">
+        <v>760.1</v>
+      </c>
+      <c r="M2">
         <v>264.0799865722656</v>
       </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
         <v>34.11000061035156</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>0.55</v>
       </c>
-      <c r="N2">
+      <c r="R2">
         <v>0.617</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>827.14</v>
@@ -557,205 +602,265 @@
         <v>42.41</v>
       </c>
       <c r="D3">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="E3">
         <v>203.85</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>51.54</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>152.31</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>3004.88</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1226.06005859375</v>
       </c>
-      <c r="I3">
+      <c r="J3">
+        <v>1062.17</v>
+      </c>
+      <c r="K3">
+        <v>1114.55</v>
+      </c>
+      <c r="L3">
+        <v>992.36</v>
+      </c>
+      <c r="M3">
         <v>346.96</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
         <v>24.12</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>0.55</v>
       </c>
-      <c r="N3">
+      <c r="R3">
         <v>0.517</v>
       </c>
-      <c r="O3">
+      <c r="S3">
         <v>-18.62</v>
       </c>
-      <c r="P3">
+      <c r="T3">
         <v>6.43</v>
       </c>
-      <c r="Q3">
+      <c r="U3">
+        <v>20.84</v>
+      </c>
+      <c r="V3">
         <v>4.35</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>835.09</v>
+        <v>818.5</v>
       </c>
       <c r="C4">
-        <v>43.93</v>
+        <v>43.3</v>
       </c>
       <c r="D4">
-        <v>206.5</v>
+        <v>92.08</v>
       </c>
       <c r="E4">
-        <v>48.78</v>
+        <v>212.98</v>
       </c>
       <c r="F4">
-        <v>157.72</v>
+        <v>37.62</v>
       </c>
       <c r="G4">
-        <v>3076.51</v>
+        <v>175.36</v>
       </c>
       <c r="H4">
+        <v>2991.47</v>
+      </c>
+      <c r="I4">
         <v>1226.06005859375</v>
       </c>
-      <c r="I4">
-        <v>280.67</v>
-      </c>
       <c r="J4">
-        <v>0</v>
+        <v>1109.73</v>
       </c>
       <c r="K4">
-        <v>23.76</v>
+        <v>1114.54</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1026.3</v>
       </c>
       <c r="M4">
+        <v>203.34</v>
+      </c>
+      <c r="N4">
+        <v>7.72</v>
+      </c>
+      <c r="O4">
+        <v>27.17</v>
+      </c>
+      <c r="P4">
+        <v>10.89999961853027</v>
+      </c>
+      <c r="Q4">
         <v>0.55</v>
       </c>
-      <c r="N4">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="O4">
-        <v>-19.76</v>
-      </c>
-      <c r="P4">
-        <v>7.95</v>
-      </c>
-      <c r="Q4">
-        <v>0.95</v>
+      <c r="R4">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="S4">
+        <v>-17.38</v>
+      </c>
+      <c r="T4">
+        <v>7.32</v>
+      </c>
+      <c r="U4">
+        <v>23.88</v>
+      </c>
+      <c r="V4">
+        <v>-10.13</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B5">
-        <v>786.3200000000001</v>
+        <v>793.74</v>
       </c>
       <c r="C5">
-        <v>42.3</v>
+        <v>42.47</v>
       </c>
       <c r="D5">
-        <v>191.18</v>
+        <v>89.06</v>
       </c>
       <c r="E5">
-        <v>53.9</v>
+        <v>196.3</v>
       </c>
       <c r="F5">
-        <v>137.28</v>
+        <v>39.83</v>
       </c>
       <c r="G5">
-        <v>2930.5</v>
+        <v>156.47</v>
       </c>
       <c r="H5">
+        <v>2921.88</v>
+      </c>
+      <c r="I5">
         <v>1226.06005859375</v>
       </c>
-      <c r="I5">
-        <v>266.41</v>
-      </c>
       <c r="J5">
-        <v>0</v>
+        <v>1081.76</v>
       </c>
       <c r="K5">
-        <v>22.99</v>
+        <v>1114.54</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>992.64</v>
       </c>
       <c r="M5">
-        <v>0.081</v>
+        <v>276.06</v>
       </c>
       <c r="N5">
-        <v>0.345</v>
+        <v>18.27</v>
       </c>
       <c r="O5">
-        <v>-12.77</v>
+        <v>25.95</v>
       </c>
       <c r="P5">
-        <v>6.32</v>
+        <v>11.71000003814697</v>
       </c>
       <c r="Q5">
-        <v>13.79</v>
+        <v>0.075</v>
+      </c>
+      <c r="R5">
+        <v>0.341</v>
+      </c>
+      <c r="S5">
+        <v>-13.83</v>
+      </c>
+      <c r="T5">
+        <v>6.49</v>
+      </c>
+      <c r="U5">
+        <v>20.86</v>
+      </c>
+      <c r="V5">
+        <v>1.73</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6">
-        <v>666.2</v>
+        <v>669.1</v>
       </c>
       <c r="C6">
         <v>41.39</v>
       </c>
       <c r="D6">
-        <v>202.57</v>
+        <v>85.44</v>
       </c>
       <c r="E6">
+        <v>203.53</v>
+      </c>
+      <c r="F6">
         <v>34.27</v>
       </c>
-      <c r="F6">
-        <v>168.31</v>
-      </c>
       <c r="G6">
-        <v>2535.93</v>
+        <v>169.26</v>
       </c>
       <c r="H6">
+        <v>2542.78</v>
+      </c>
+      <c r="I6">
         <v>1226.06005859375</v>
       </c>
-      <c r="I6">
+      <c r="J6">
+        <v>1008.64</v>
+      </c>
+      <c r="K6">
+        <v>1114.55</v>
+      </c>
+      <c r="L6">
+        <v>952.3200000000001</v>
+      </c>
+      <c r="M6">
         <v>299.21</v>
       </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>19.97</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
         <v>0.55</v>
       </c>
-      <c r="N6">
+      <c r="R6">
         <v>0.506</v>
       </c>
-      <c r="O6">
-        <v>4.46</v>
-      </c>
-      <c r="P6">
+      <c r="S6">
+        <v>4.04</v>
+      </c>
+      <c r="T6">
         <v>5.41</v>
       </c>
-      <c r="Q6">
-        <v>-5.7</v>
+      <c r="U6">
+        <v>17.24</v>
+      </c>
+      <c r="V6">
+        <v>-6.3</v>
       </c>
     </row>
   </sheetData>
